--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/5536-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/5536-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0BAAC63-551E-4DD6-A1B1-59F9F7DB6388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{45C014CF-3872-4340-A43F-F0724671440C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{4F9B0164-BB11-41BF-BDF3-6F4965392C1E}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{9F1EDB69-0C49-4C02-AEC7-923AC8283D20}"/>
   </bookViews>
   <sheets>
     <sheet name="5536-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1513,25 +1513,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB36F304-684F-4176-8283-755A2518BDFD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{950B05F0-2689-4771-ACAE-803821159358}">
   <dimension ref="A1:R30"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1559,7 +1559,7 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1589,7 +1589,7 @@
       <c r="Q2" s="36"/>
       <c r="R2" s="37"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1685,7 +1685,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>2026</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="44"/>
       <c r="C6" s="46"/>
@@ -1765,7 +1765,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="51">
         <v>2025</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="53">
         <v>2024</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="51">
         <v>2023</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>8.3800000000000008</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="53">
         <v>2022</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="51">
         <v>2021</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="53">
         <v>2020</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="51">
         <v>2019</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>8.1300000000000008</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="53">
         <v>2018</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
         <v>2017</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="53">
         <v>2016</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="51">
         <v>2015</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="53">
         <v>2014</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>8.93</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="51">
         <v>2013</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="53">
         <v>2012</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>8.26</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="51">
         <v>2011</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="53">
         <v>2010</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="51" t="s">
         <v>40</v>
       </c>
